--- a/out/Attention-Mamba1_repeat_4_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7562253596518723</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7562253596518723</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7562253596518723</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7562253596518723</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>4.596122136721797</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.808654750767164e-05</v>
+        <v>-0.0003418900619039778</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.015507797272852</v>
+        <v>3.941487474503797</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.032585386332869</v>
+        <v>7.889067777327875</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1522799241534852</v>
+        <v>0.5910436062027098</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.320274486219957</v>
+        <v>5.124377542311797</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1903993971341759</v>
+        <v>0.7389968776464874</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7562253596518723</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.54881765302517</v>
+        <v>6.01142150787509</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2729366328414245</v>
+        <v>1.059348519486222</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>4.596122136721797</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.90439918456769</v>
+        <v>7.391538717847709</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2919881339107572</v>
+        <v>1.133292732263334</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.215459540539432</v>
+        <v>8.598855342662061</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3094493067578896</v>
+        <v>1.201061870469419</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.542391418816434</v>
+        <v>9.867772888131244</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1396487167619065</v>
+        <v>0.5420175497264333</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.511982394437883</v>
+        <v>9.749746562752724</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06744330417367587</v>
+        <v>0.2617697027703341</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.507112069648309</v>
+        <v>9.730843402744782</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03213533941932296</v>
+        <v>0.1247254699899119</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.503884597633051</v>
+        <v>9.718316758518943</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009519389336447392</v>
+        <v>0.03695492354617681</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.490755894252969</v>
+        <v>9.667369006372391</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006295020030424058</v>
+        <v>0.02444478433527624</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.493822567733887</v>
+        <v>9.679283629046649</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003219420919834627</v>
+        <v>0.01250992513865628</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.493962642714194</v>
+        <v>9.679841707677873</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001643912581159883</v>
+        <v>0.006396364532109703</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.494030136116772</v>
+        <v>9.680118074111546</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006148887471728657</v>
+        <v>0.002401894036641896</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.493614501725456</v>
+        <v>9.678519640511388</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000333252450676027</v>
+        <v>0.001306759503841178</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.493665015250374</v>
+        <v>9.678729924668998</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001579196398644573</v>
+        <v>0.0006268103106938711</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.493647388194576</v>
+        <v>9.678675956330659</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.536342197837412e-05</v>
+        <v>0.000385630181621711</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.493681103769836</v>
+        <v>9.678821095496229</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.749782703175804e-05</v>
+        <v>0.0001998444623396049</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.493680723158569</v>
+        <v>9.678833942753206</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.097642140041462e-05</v>
+        <v>9.391021994773259e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.49367411529453</v>
+        <v>9.678822790189271</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.162890291091525e-05</v>
+        <v>5.895731888813557e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.493676385243452</v>
+        <v>9.678845751531279</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>2.41402819409171e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.493669899016776</v>
+        <v>9.678835032551401</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>7.35242988982542e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.493663940418637</v>
+        <v>9.678826607376267</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>1.675769385467227e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.49365927115</v>
+        <v>9.678822682929461</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-2.093548687745288e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.493653982002438</v>
+        <v>9.678816671502869</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-3.107779831880603e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.493653959268137</v>
+        <v>9.678811578260735</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.493654277548353</v>
+        <v>9.678807213286767</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.493655368794811</v>
+        <v>9.678808304533222</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.493654679187674</v>
+        <v>9.678807614926086</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.493654709500076</v>
+        <v>9.678807645238489</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.493654520047566</v>
+        <v>9.678807455785979</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.493654573094269</v>
+        <v>9.678807508832682</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.493654626140972</v>
+        <v>9.678807561879383</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.493654588250469</v>
+        <v>9.678807523988882</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.493654459422763</v>
+        <v>9.678807395161176</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.493654315438855</v>
+        <v>9.678807251177268</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.493654156298747</v>
+        <v>9.678807092037159</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.49365420934545</v>
+        <v>9.678807145083864</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.493654156298747</v>
+        <v>9.678807092037159</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.493654156298747</v>
+        <v>9.678807092037159</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.493653974424337</v>
+        <v>9.67880691016275</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.493654141142546</v>
+        <v>9.678807076880959</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.493654338173156</v>
+        <v>9.67880727391157</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.493654179033049</v>
+        <v>9.678807114771461</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.49365421692355</v>
+        <v>9.678807152661962</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.493654413954161</v>
+        <v>9.678807349692574</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.493654391219859</v>
+        <v>9.678807326958273</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.493654239657852</v>
+        <v>9.678807175396264</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.493654163876847</v>
+        <v>9.678807099615261</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.493654262392153</v>
+        <v>9.678807198130565</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.493654269970253</v>
+        <v>9.678807205708665</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.493654535203767</v>
+        <v>9.678807470942179</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.493654239657852</v>
+        <v>9.678807175396264</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.493654482157064</v>
+        <v>9.678807417895477</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.493654565516168</v>
+        <v>9.678807501254582</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.493654398797959</v>
+        <v>9.678807334536371</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.493654588250469</v>
+        <v>9.678807523988882</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.493654239657852</v>
+        <v>9.678807175396264</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.493654035049141</v>
+        <v>9.678806970787553</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.493654148720647</v>
+        <v>9.678807084459059</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.493654163876847</v>
+        <v>9.678807099615261</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.493653928955735</v>
+        <v>9.678806864694149</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.493653989580538</v>
+        <v>9.67880692531895</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.493653860752832</v>
+        <v>9.678806796491244</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.493653997158638</v>
+        <v>9.678806932897052</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.493654171454948</v>
+        <v>9.678807107193361</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.493654315438855</v>
+        <v>9.678807251177268</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.493654148720647</v>
+        <v>9.678807084459059</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.493654141142546</v>
+        <v>9.678807076880959</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.493653853174731</v>
+        <v>9.678806788913144</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.493653868330932</v>
+        <v>9.678806804069344</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.493654095673944</v>
+        <v>9.678807031412358</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.493654080517743</v>
+        <v>9.678807016256155</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.493654186611149</v>
+        <v>9.678807122349562</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.493653913799534</v>
+        <v>9.678806849537946</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.49365401231484</v>
+        <v>9.678806948053252</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.493654163876847</v>
+        <v>9.678807099615261</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.493654179033049</v>
+        <v>9.678807114771461</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.493654156298747</v>
+        <v>9.678807092037159</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.493654239657852</v>
+        <v>9.678807175396264</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.493654338173156</v>
+        <v>9.67880727391157</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.493654171454948</v>
+        <v>9.678807107193361</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.493654156298747</v>
+        <v>9.678807092037159</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.493654125986346</v>
+        <v>9.678807061724758</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.493654110830144</v>
+        <v>9.678807046568558</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.493654148720647</v>
+        <v>9.678807084459059</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.493654163876847</v>
+        <v>9.678807099615261</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.493654156298747</v>
+        <v>9.678807092037159</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>4.596122136721797</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.808654750767164e-05</v>
+        <v>-8.834468875301536e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.015507797272852</v>
+        <v>1.018483708925396</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.032585386332869</v>
+        <v>2.038541961415759</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1522799241534852</v>
+        <v>0.1527261980710141</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.320274486219957</v>
+        <v>1.324143551884523</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1903993971341759</v>
+        <v>0.1909573847392291</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.7114398355877154</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.54881765302517</v>
+        <v>1.553356490853724</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2729366328414245</v>
+        <v>0.2737366681019878</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.90439918456769</v>
+        <v>1.90998009460534</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2919881339107572</v>
+        <v>0.2928436651088622</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.596122136721797</v>
+        <v>3.04</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.215459540539432</v>
+        <v>2.221951862687504</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3094493067578896</v>
+        <v>0.3103552596409339</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.596122136721797</v>
+        <v>3.04</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.542391418816434</v>
+        <v>2.549841656881963</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1396487167619065</v>
+        <v>0.1400575564484108</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.511982394437883</v>
+        <v>2.519343462166223</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06744330417367587</v>
+        <v>0.06764139821809133</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1562253596518723</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.507112069648309</v>
+        <v>2.514458832423177</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03213533941932296</v>
+        <v>0.03222972533385179</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>4.596122136721797</v>
+        <v>0.9114398355877152</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.503884597633051</v>
+        <v>2.511221880878427</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009519389336447392</v>
+        <v>0.009547000474285734</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.7114398355877154</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.490755894252969</v>
+        <v>2.498054631819729</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006295020030424058</v>
+        <v>0.006313283744274845</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.493822567733887</v>
+        <v>2.501130444981623</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003219420919834627</v>
+        <v>0.003229260471008978</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.493962642714194</v>
+        <v>2.501270962668613</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001643912581159883</v>
+        <v>0.001648945891847184</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.494030136116772</v>
+        <v>2.501338677288127</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006148887471728657</v>
+        <v>0.0006171594019244146</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.493614501725456</v>
+        <v>2.500921789734879</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000333252450676027</v>
+        <v>0.0003340774566532856</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.493665015250374</v>
+        <v>2.500972438658638</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.493647388194576</v>
+        <v>2.500954781290438</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.536342197837412e-05</v>
+        <v>9.634737709580916e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.493681103769836</v>
+        <v>2.500988685120275</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.493680723158569</v>
+        <v>2.500988304509007</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.49367411529453</v>
+        <v>2.500981696644968</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.493676385243452</v>
+        <v>2.50098396659389</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.493669899016776</v>
+        <v>2.500977480367214</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.493663940418637</v>
+        <v>2.500971521769075</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.49365927115</v>
+        <v>2.500966852500438</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.493653982002438</v>
+        <v>2.500961563352877</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.7114398355877154</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.493653959268137</v>
+        <v>2.500961540618575</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.493654277548353</v>
+        <v>2.500961858898791</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>4.596122136721797</v>
+        <v>3.04</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.493655368794811</v>
+        <v>2.500962950145249</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.493654679187674</v>
+        <v>2.500962260538113</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.493654709500076</v>
+        <v>2.500962290850514</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.493654520047566</v>
+        <v>2.500962101398004</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.493654573094269</v>
+        <v>2.500962154444707</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.493654626140972</v>
+        <v>2.50096220749141</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.493654588250469</v>
+        <v>2.500962169600908</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.493654459422763</v>
+        <v>2.500962040773201</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.493654315438855</v>
+        <v>2.500961896789294</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.493654156298747</v>
+        <v>2.500961737649185</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.49365420934545</v>
+        <v>2.500961790695888</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.493654156298747</v>
+        <v>2.500961737649185</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.493654156298747</v>
+        <v>2.500961737649185</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.493653974424337</v>
+        <v>2.500961555774776</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.493654141142546</v>
+        <v>2.500961722492984</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.493654338173156</v>
+        <v>2.500961919523595</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.493654179033049</v>
+        <v>2.500961760383487</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.49365421692355</v>
+        <v>2.500961798273988</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.493654413954161</v>
+        <v>2.500961995304599</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.493654391219859</v>
+        <v>2.500961972570298</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.493654239657852</v>
+        <v>2.50096182100829</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.493654163876847</v>
+        <v>2.500961745227286</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.493654262392153</v>
+        <v>2.500961843742591</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.493654269970253</v>
+        <v>2.500961851320691</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.493654535203767</v>
+        <v>2.500962116554205</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.493654239657852</v>
+        <v>2.50096182100829</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.493654482157064</v>
+        <v>2.500962063507502</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.493654565516168</v>
+        <v>2.500962146866606</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>4.596122136721797</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.493654398797959</v>
+        <v>2.500961980148398</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.493654588250469</v>
+        <v>2.500962169600908</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.493654239657852</v>
+        <v>2.50096182100829</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.493654035049141</v>
+        <v>2.500961616399579</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.493654148720647</v>
+        <v>2.500961730071085</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.493654163876847</v>
+        <v>2.500961745227286</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.493653928955735</v>
+        <v>2.500961510306174</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.493653989580538</v>
+        <v>2.500961570930976</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.493653860752832</v>
+        <v>2.50096144210327</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.493653997158638</v>
+        <v>2.500961578509077</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.493654171454948</v>
+        <v>2.500961752805386</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.493654315438855</v>
+        <v>2.500961896789294</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.493654148720647</v>
+        <v>2.500961730071085</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.493654141142546</v>
+        <v>2.500961722492984</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.493653853174731</v>
+        <v>2.500961434525169</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.493653868330932</v>
+        <v>2.500961449681371</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.493654095673944</v>
+        <v>2.500961677024382</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.493654080517743</v>
+        <v>2.500961661868181</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.493654186611149</v>
+        <v>2.500961767961587</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.493653913799534</v>
+        <v>2.500961495149973</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.49365401231484</v>
+        <v>2.500961593665278</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.493654163876847</v>
+        <v>2.500961745227286</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.493654179033049</v>
+        <v>2.500961760383487</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.493654156298747</v>
+        <v>2.500961737649185</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.493654239657852</v>
+        <v>2.50096182100829</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.493654338173156</v>
+        <v>2.500961919523595</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.493654171454948</v>
+        <v>2.500961752805386</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.493654156298747</v>
+        <v>2.500961737649185</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.493654125986346</v>
+        <v>2.500961707336784</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.493654110830144</v>
+        <v>2.500961692180583</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.493654148720647</v>
+        <v>2.500961730071085</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.493654163876847</v>
+        <v>2.500961745227286</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.493654156298747</v>
+        <v>2.500961737649185</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.002086635679006577</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.002014825120568275</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001846099272370338</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001825982704758644</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001978674903512001</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001989439129829407</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.002000162377953529</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.002189302816987038</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.002130605280399323</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.002216188237071037</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.002315308898687363</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.002337304875254631</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.002135371789336205</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.002252662554383278</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.002172311767935753</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.00233619287610054</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.002252211794257164</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.002361265942454338</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.002249782904982567</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.002158867195248604</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.001789720728993416</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001214576885104179</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001742949709296227</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.001859733834862709</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.001925276592373848</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0020583625882864</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.002194657921791077</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.001777349039912224</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.001843094825744629</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.001988762989640236</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.002026742324233055</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.00207907147705555</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.002014217898249626</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.001942949369549751</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.001084083691239357</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.00135909765958786</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.0002566315233707428</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0003369767218828201</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1528402466184268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.834468875301536e-05</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.018483708925396</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0005368683487176895</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.038541961415759</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1527261980710141</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0006556082516908646</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.324143551884523</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1909573847392291</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0009816009551286697</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7114398355877154</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.553356490853724</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2737366681019878</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0004466157406568527</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.975719917793858</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.90998009460534</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2928436651088622</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.001490060240030289</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.04</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.221951862687504</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3103552596409339</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.002785129472613335</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.04</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.549841656881963</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1400575564484108</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.003421967849135399</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.975719917793858</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.519343462166223</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06764139821809133</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0007726941257715225</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.975719917793858</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.514458832423177</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03222972533385179</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0007524378597736359</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9114398355877152</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.511221880878427</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009547000474285734</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001115124672651291</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7114398355877154</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.498054631819729</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006313283744274845</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.000580979511141777</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.501130444981623</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003229260471008978</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001631567254662514</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.501270962668613</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001648945891847184</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0007448997348546982</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.501338677288127</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006171594019244146</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0009270720183849335</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.500921789734879</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003340774566532856</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.001295136287808418</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.500972438658638</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001579196398644573</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.001551862806081772</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.500954781290438</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.634737709580916e-05</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.001206863671541214</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.500988685120275</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.749782703175804e-05</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002446426078677177</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9114398355877155</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.500988304509007</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.097642140041462e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.004120441153645515</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.975719917793858</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.500981696644968</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.162890291091525e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.001154268160462379</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.975719917793858</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.50098396659389</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001452647149562836</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.500977480367214</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.002178629860281944</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.500971521769075</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.001495398581027985</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.500966852500438</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001167954877018929</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.500961563352877</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0003713015466928482</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7114398355877154</v>
+        <v>0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.500961540618575</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.003019999712705612</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.975719917793858</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.500961858898791</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01064026169478893</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.04</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.500962950145249</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.002347929403185844</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.975719917793858</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.500962260538113</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0002418123185634613</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.500962290850514</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001838970929384232</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.500962101398004</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0008510779589414597</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.500962154444707</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00173029862344265</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.50096220749141</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002079864963889122</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.500962169600908</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001534750685095787</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.500962040773201</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.00133603997528553</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.500961896789294</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00159933790564537</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.500961737649185</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001580050215125084</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.500961790695888</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.002418728545308113</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.500961737649185</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.001926979050040245</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.500961737649185</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001352144405245781</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.500961555774776</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.0009411126375198364</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.500961722492984</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.001678137108683586</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.500961919523595</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002571480348706245</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.500961760383487</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001616952940821648</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.500961798273988</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0004697274416685104</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.500961995304599</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001434354111552238</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.500961972570298</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002351494506001472</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.50096182100829</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002365941181778908</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.500961745227286</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.002041565254330635</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.500961843742591</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.0008950140327215195</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.500961851320691</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001041319221258163</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.500962116554205</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002086637541651726</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.50096182100829</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.001238079741597176</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.500962063507502</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.002009294927120209</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.500962146866606</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.000890808179974556</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.500961980148398</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0004185270518064499</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.500962169600908</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.00162041001021862</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1528402466184268</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.50096182100829</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.002605598419904709</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.500961616399579</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.002623999491333961</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.500961730071085</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.001801088452339172</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.500961745227286</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.001878596842288971</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.500961510306174</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.002296457067131996</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.500961570930976</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.002764301374554634</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.50096144210327</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.000776488333940506</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.500961578509077</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.001867623999714851</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.500961752805386</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002317223697900772</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.500961896789294</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002223711460828781</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.500961730071085</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.001803113147616386</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.500961722492984</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.002504343166947365</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.500961434525169</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002664262428879738</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.500961449681371</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002560893073678017</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.500961677024382</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002070769667625427</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.500961661868181</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.00245596282184124</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.500961767961587</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002709044143557549</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.500961495149973</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002554850652813911</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.500961593665278</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002411747351288795</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.500961745227286</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002462657168507576</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.500961760383487</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002371931448578835</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.500961737649185</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002061916515231133</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.50096182100829</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002536667510867119</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.500961919523595</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002701656892895699</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.500961752805386</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0025810357183218</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.500961737649185</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002346958965063095</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.500961707336784</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002332238480448723</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.500961692180583</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002508630976080894</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.500961730071085</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002276597544550896</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.3700000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.500961745227286</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001711057499051094</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.500961737649185</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.002086635679006577</v>
+        <v>-0.002086624503135681</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.002014825120568275</v>
+        <v>-0.002014828845858574</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.001846099272370338</v>
+        <v>-0.001846106722950935</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001978674903512001</v>
+        <v>-0.001978671178221703</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001989439129829407</v>
+        <v>-0.001989444717764854</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.002000162377953529</v>
+        <v>-0.002000182867050171</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.002189302816987038</v>
+        <v>-0.002189306542277336</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.002130605280399323</v>
+        <v>-0.002130599692463875</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.002315308898687363</v>
+        <v>-0.002315318211913109</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.002337304875254631</v>
+        <v>-0.002337334677577019</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.002135371789336205</v>
+        <v>-0.002135362476110458</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.2599999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.002252662554383278</v>
+        <v>-0.002252668142318726</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.2599999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.002172311767935753</v>
+        <v>-0.002172293141484261</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.2599999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.00233619287610054</v>
+        <v>-0.002336191013455391</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.2599999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.002249782904982567</v>
+        <v>-0.002249779179692268</v>
       </c>
       <c r="JB20" t="n">
         <v>0.02000000000000007</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.002158867195248604</v>
+        <v>-0.002158826217055321</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.001789720728993416</v>
+        <v>-0.001789722591638565</v>
       </c>
       <c r="JB22" t="n">
         <v>0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.001214576885104179</v>
+        <v>-0.001214582473039627</v>
       </c>
       <c r="JB23" t="n">
         <v>0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.001859733834862709</v>
+        <v>-0.001859737560153008</v>
       </c>
       <c r="JB25" t="n">
         <v>0.8599999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0020583625882864</v>
+        <v>-0.002058332785964012</v>
       </c>
       <c r="JB27" t="n">
         <v>0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.002194657921791077</v>
+        <v>-0.002194646745920181</v>
       </c>
       <c r="JB28" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.001777349039912224</v>
+        <v>-0.001777360215783119</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.001843094825744629</v>
+        <v>-0.001843107864260674</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.001988762989640236</v>
+        <v>-0.001988789066672325</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.002026742324233055</v>
+        <v>-0.002026734873652458</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.16</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.00207907147705555</v>
+        <v>-0.00207904540002346</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.002014217898249626</v>
+        <v>-0.002014210447669029</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.16</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.001942949369549751</v>
+        <v>-0.001942941918969154</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.001084083691239357</v>
+        <v>-0.001084098592400551</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.00135909765958786</v>
+        <v>0.001359095796942711</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.0002566315233707428</v>
+        <v>-0.0002566184848546982</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0003369767218828201</v>
+        <v>-0.0003370046615600586</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0006556082516908646</v>
+        <v>-0.0006556157022714615</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0009816009551286697</v>
+        <v>-0.0009816233068704605</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.0004466157406568527</v>
+        <v>0.0004466045647859573</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.001490060240030289</v>
+        <v>0.001490062102675438</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.002785129472613335</v>
+        <v>0.002785118296742439</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.003421967849135399</v>
+        <v>0.003421971574425697</v>
       </c>
       <c r="JB46" t="n">
         <v>0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0007726941257715225</v>
+        <v>-0.0007726904004812241</v>
       </c>
       <c r="JB47" t="n">
         <v>0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.0007524378597736359</v>
+        <v>0.0007524695247411728</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.02000000000000007</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001115124672651291</v>
+        <v>-0.001115132123231888</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.3</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.000580979511141777</v>
+        <v>-0.0005809497088193893</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.4399999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.001631567254662514</v>
+        <v>-0.001631548628211021</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0007448997348546982</v>
+        <v>-0.0007449332624673843</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.0009270720183849335</v>
+        <v>-0.0009270776063203812</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.8599999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.001295136287808418</v>
+        <v>-0.001295130699872971</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.8599999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.001551862806081772</v>
+        <v>-0.001551860943436623</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.001206863671541214</v>
+        <v>-0.00120687298476696</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.002446426078677177</v>
+        <v>-0.002446413040161133</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.004120441153645515</v>
+        <v>0.004120420664548874</v>
       </c>
       <c r="JB58" t="n">
         <v>0.1600000000000001</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.001154268160462379</v>
+        <v>0.001154275611042976</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1600000000000001</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.001452647149562836</v>
+        <v>-0.001452622935175896</v>
       </c>
       <c r="JB60" t="n">
         <v>0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.002178629860281944</v>
+        <v>-0.002178620547056198</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.1199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.001495398581027985</v>
+        <v>-0.001495366916060448</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.2599999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.001167954877018929</v>
+        <v>-0.001167969778180122</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.5799999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0003713015466928482</v>
+        <v>-0.0003712866455316544</v>
       </c>
       <c r="JB64" t="n">
         <v>0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.003019999712705612</v>
+        <v>0.003019994124770164</v>
       </c>
       <c r="JB65" t="n">
         <v>0.5799999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.01064026169478893</v>
+        <v>0.01064023561775684</v>
       </c>
       <c r="JB66" t="n">
         <v>0.5799999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.002347929403185844</v>
+        <v>0.002347903326153755</v>
       </c>
       <c r="JB67" t="n">
         <v>0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.0002418123185634613</v>
+        <v>-0.0002418104559183121</v>
       </c>
       <c r="JB68" t="n">
         <v>0.16</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.001838970929384232</v>
+        <v>-0.001838983967900276</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0008510779589414597</v>
+        <v>-0.0008510369807481766</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.00173029862344265</v>
+        <v>-0.001730279996991158</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.002079864963889122</v>
+        <v>-0.002079866826534271</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.001534750685095787</v>
+        <v>-0.001534756273031235</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.00133603997528553</v>
+        <v>-0.001336051151156425</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.00159933790564537</v>
+        <v>-0.001599345356225967</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.001580050215125084</v>
+        <v>-0.001580042764544487</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.002418728545308113</v>
+        <v>-0.002418739721179008</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.001926979050040245</v>
+        <v>-0.001926984637975693</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001352144405245781</v>
+        <v>-0.001352163031697273</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.0009411126375198364</v>
+        <v>-0.0009411182254552841</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.001678137108683586</v>
+        <v>-0.001678133383393288</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002571480348706245</v>
+        <v>-0.002571491524577141</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>4.989783636080341</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.001616952940821648</v>
+        <v>-0.001616949215531349</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>4.989783673970843</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.0004697274416685104</v>
+        <v>-0.0004697423428297043</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>4.989783871001453</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001434354111552238</v>
+        <v>-0.00143435038626194</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>4.989783848267152</v>
@@ -69314,7 +69314,7 @@
         <v>-0.002351494506001472</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>4.989783696705144</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.002365941181778908</v>
+        <v>-0.00236593559384346</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.2599999999999998</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.002041565254330635</v>
+        <v>-0.002041557803750038</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>4.989783719439446</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.0008950140327215195</v>
+        <v>-0.0008950065821409225</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>4.989783727017546</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.001041319221258163</v>
+        <v>-0.001041321083903313</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>4.98978399225106</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002086637541651726</v>
+        <v>-0.002086643129587173</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>4.989783696705144</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.001238079741597176</v>
+        <v>-0.001238072291016579</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>4.989783939204357</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.002009294927120209</v>
+        <v>-0.00200926885008812</v>
       </c>
       <c r="JB93" t="n">
         <v>0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.000890808179974556</v>
+        <v>0.0008908119052648544</v>
       </c>
       <c r="JB94" t="n">
         <v>0.1600000000000001</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.0004185270518064499</v>
+        <v>-0.0004185661673545837</v>
       </c>
       <c r="JB95" t="n">
         <v>0.1600000000000001</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.00162041001021862</v>
+        <v>-0.001620419323444366</v>
       </c>
       <c r="JB96" t="n">
         <v>0.16</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.002605598419904709</v>
+        <v>-0.002605602145195007</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.1199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.002623999491333961</v>
+        <v>-0.002623984590172768</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.001801088452339172</v>
+        <v>-0.001801090314984322</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.001878596842288971</v>
+        <v>-0.001878593116998672</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.002296457067131996</v>
+        <v>-0.002296460792422295</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.002764301374554634</v>
+        <v>-0.002764299511909485</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.000776488333940506</v>
+        <v>-0.0007764715701341629</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.001867623999714851</v>
+        <v>-0.001867661252617836</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.1199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.002317223697900772</v>
+        <v>-0.002317225560545921</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.1199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.002223711460828781</v>
+        <v>-0.00222371332347393</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.3999999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.001803113147616386</v>
+        <v>-0.001803105697035789</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.002504343166947365</v>
+        <v>-0.00250433012843132</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002664262428879738</v>
+        <v>-0.002664258703589439</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.002560893073678017</v>
+        <v>-0.002560881897807121</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.00245596282184124</v>
+        <v>-0.002455942332744598</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002709044143557549</v>
+        <v>-0.002709068357944489</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002554850652813911</v>
+        <v>-0.002554835751652718</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002411747351288795</v>
+        <v>-0.00241176038980484</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002462657168507576</v>
+        <v>-0.002462649717926979</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.002371931448578835</v>
+        <v>-0.002371920272707939</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002061916515231133</v>
+        <v>-0.00206189788877964</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.002536667510867119</v>
+        <v>-0.002536622807383537</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002701656892895699</v>
+        <v>-0.002701641991734505</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.0025810357183218</v>
+        <v>-0.002581005915999413</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.002346958965063095</v>
+        <v>-0.002346964552998543</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.002332238480448723</v>
+        <v>-0.002332231029868126</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.2599999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.002508630976080894</v>
+        <v>-0.002508608624339104</v>
       </c>
       <c r="JB124" t="n">
         <v>0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002276597544550896</v>
+        <v>-0.002276616171002388</v>
       </c>
       <c r="JB125" t="n">
         <v>0.3700000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.001711057499051094</v>
+        <v>-0.001711050048470497</v>
       </c>
       <c r="JB126" t="n">
         <v>0.7200000000000004</v>
